--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="186">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>author permet d’enregistrer un auteur du document.</t>
+    <t>L'élément de l'en-tête du CDA author permet d’enregistrer un auteur du document.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -413,6 +413,9 @@
 </t>
   </si>
   <si>
+    <t>Rôle fonctionnel de l'auteur. A utiliser uniquement si l'auteur est un professionnel.</t>
+  </si>
+  <si>
     <t>Author.functionCode.nullFlavor</t>
   </si>
   <si>
@@ -508,6 +511,9 @@
 </t>
   </si>
   <si>
+    <t>Description du rôle fonctionnel de l'auteur.</t>
+  </si>
+  <si>
     <t>The text or phrase used as the basis for the coding.</t>
   </si>
   <si>
@@ -553,6 +559,9 @@
 </t>
   </si>
   <si>
+    <t>Horodatage de la participation de l’auteur</t>
+  </si>
+  <si>
     <t>Author.time.nullFlavor</t>
   </si>
   <si>
@@ -574,6 +583,9 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedAuthor {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-author}
 </t>
+  </si>
+  <si>
+    <t>Identification de l’auteur</t>
   </si>
 </sst>
 </file>
@@ -2273,7 +2285,9 @@
       <c r="K14" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2344,10 +2358,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2445,10 +2459,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2477,7 +2491,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2508,7 +2522,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2526,7 +2540,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2546,17 +2560,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>75</v>
@@ -2578,7 +2592,7 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2629,7 +2643,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2649,17 +2663,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
@@ -2681,7 +2695,7 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2732,7 +2746,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2752,17 +2766,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2784,7 +2798,7 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2835,7 +2849,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2855,17 +2869,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2887,7 +2901,7 @@
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2938,7 +2952,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2958,10 +2972,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2984,11 +2998,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3039,7 +3053,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3059,10 +3073,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3089,7 +3103,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3140,7 +3154,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3160,17 +3174,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3188,11 +3202,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L23" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="M23" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3243,7 +3259,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3263,17 +3279,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3291,11 +3307,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3346,7 +3362,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3366,17 +3382,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3394,11 +3410,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3449,7 +3465,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3469,10 +3485,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3495,9 +3511,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3548,7 +3566,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3568,10 +3586,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3669,10 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3695,11 +3713,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3750,7 +3768,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3770,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3796,9 +3814,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="L29" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3849,7 +3869,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
